--- a/outputs/player_points_by_team_game.xlsx
+++ b/outputs/player_points_by_team_game.xlsx
@@ -1955,7 +1955,7 @@
         <v>70</v>
       </c>
       <c r="P23" t="n">
-        <v>107</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
         <v>0</v>
@@ -1967,7 +1967,7 @@
         <v>0</v>
       </c>
       <c r="T23" t="n">
-        <v>646</v>
+        <v>539</v>
       </c>
     </row>
     <row r="24">
@@ -2021,7 +2021,7 @@
         <v>76</v>
       </c>
       <c r="P24" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
         <v>0</v>
@@ -2033,7 +2033,7 @@
         <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>157</v>
+        <v>127</v>
       </c>
     </row>
     <row r="25">
@@ -2087,7 +2087,7 @@
         <v>27</v>
       </c>
       <c r="P25" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>
@@ -2099,7 +2099,7 @@
         <v>0</v>
       </c>
       <c r="T25" t="n">
-        <v>290</v>
+        <v>258</v>
       </c>
     </row>
     <row r="26">
@@ -2219,7 +2219,7 @@
         <v>23</v>
       </c>
       <c r="P27" t="n">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="Q27" t="n">
         <v>0</v>
@@ -2231,7 +2231,7 @@
         <v>0</v>
       </c>
       <c r="T27" t="n">
-        <v>384</v>
+        <v>328</v>
       </c>
     </row>
     <row r="28">
@@ -2417,7 +2417,7 @@
         <v>77</v>
       </c>
       <c r="P30" t="n">
-        <v>91</v>
+        <v>0</v>
       </c>
       <c r="Q30" t="n">
         <v>0</v>
@@ -2429,7 +2429,7 @@
         <v>0</v>
       </c>
       <c r="T30" t="n">
-        <v>903</v>
+        <v>812</v>
       </c>
     </row>
     <row r="31">
@@ -2483,7 +2483,7 @@
         <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>83</v>
+        <v>0</v>
       </c>
       <c r="Q31" t="n">
         <v>0</v>
@@ -2495,7 +2495,7 @@
         <v>0</v>
       </c>
       <c r="T31" t="n">
-        <v>323</v>
+        <v>240</v>
       </c>
     </row>
     <row r="32">
@@ -2549,7 +2549,7 @@
         <v>66</v>
       </c>
       <c r="P32" t="n">
-        <v>91</v>
+        <v>0</v>
       </c>
       <c r="Q32" t="n">
         <v>0</v>
@@ -2561,7 +2561,7 @@
         <v>0</v>
       </c>
       <c r="T32" t="n">
-        <v>427</v>
+        <v>336</v>
       </c>
     </row>
     <row r="33">
@@ -2615,7 +2615,7 @@
         <v>56</v>
       </c>
       <c r="P33" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q33" t="n">
         <v>0</v>
@@ -2627,7 +2627,7 @@
         <v>0</v>
       </c>
       <c r="T33" t="n">
-        <v>140</v>
+        <v>138</v>
       </c>
     </row>
     <row r="34">
@@ -2681,7 +2681,7 @@
         <v>126</v>
       </c>
       <c r="P34" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="Q34" t="n">
         <v>0</v>
@@ -2693,7 +2693,7 @@
         <v>0</v>
       </c>
       <c r="T34" t="n">
-        <v>349</v>
+        <v>279</v>
       </c>
     </row>
     <row r="35">
@@ -3011,7 +3011,7 @@
         <v>14</v>
       </c>
       <c r="P39" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="Q39" t="n">
         <v>0</v>
@@ -3023,7 +3023,7 @@
         <v>0</v>
       </c>
       <c r="T39" t="n">
-        <v>79</v>
+        <v>44</v>
       </c>
     </row>
     <row r="40">
@@ -3077,7 +3077,7 @@
         <v>0</v>
       </c>
       <c r="P40" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="Q40" t="n">
         <v>0</v>
@@ -3089,7 +3089,7 @@
         <v>0</v>
       </c>
       <c r="T40" t="n">
-        <v>415</v>
+        <v>403</v>
       </c>
     </row>
     <row r="41">
@@ -3209,7 +3209,7 @@
         <v>16</v>
       </c>
       <c r="P42" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="Q42" t="n">
         <v>0</v>
@@ -3221,7 +3221,7 @@
         <v>0</v>
       </c>
       <c r="T42" t="n">
-        <v>459</v>
+        <v>447</v>
       </c>
     </row>
     <row r="43">
@@ -4661,7 +4661,7 @@
         <v>29</v>
       </c>
       <c r="P64" t="n">
-        <v>99</v>
+        <v>0</v>
       </c>
       <c r="Q64" t="n">
         <v>0</v>
@@ -4673,7 +4673,7 @@
         <v>0</v>
       </c>
       <c r="T64" t="n">
-        <v>550</v>
+        <v>451</v>
       </c>
     </row>
     <row r="65">
@@ -4727,7 +4727,7 @@
         <v>24</v>
       </c>
       <c r="P65" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="Q65" t="n">
         <v>0</v>
@@ -4739,7 +4739,7 @@
         <v>0</v>
       </c>
       <c r="T65" t="n">
-        <v>430</v>
+        <v>395</v>
       </c>
     </row>
     <row r="66">
@@ -4859,7 +4859,7 @@
         <v>66</v>
       </c>
       <c r="P67" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Q67" t="n">
         <v>0</v>
@@ -4871,7 +4871,7 @@
         <v>0</v>
       </c>
       <c r="T67" t="n">
-        <v>709</v>
+        <v>705</v>
       </c>
     </row>
     <row r="68">
@@ -4925,7 +4925,7 @@
         <v>12</v>
       </c>
       <c r="P68" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="Q68" t="n">
         <v>0</v>
@@ -4937,7 +4937,7 @@
         <v>0</v>
       </c>
       <c r="T68" t="n">
-        <v>357</v>
+        <v>322</v>
       </c>
     </row>
     <row r="69">
@@ -4991,7 +4991,7 @@
         <v>14</v>
       </c>
       <c r="P69" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="Q69" t="n">
         <v>0</v>
@@ -5003,7 +5003,7 @@
         <v>0</v>
       </c>
       <c r="T69" t="n">
-        <v>546</v>
+        <v>505</v>
       </c>
     </row>
     <row r="70">
@@ -5057,7 +5057,7 @@
         <v>54</v>
       </c>
       <c r="P70" t="n">
-        <v>-4</v>
+        <v>0</v>
       </c>
       <c r="Q70" t="n">
         <v>0</v>
@@ -5069,7 +5069,7 @@
         <v>0</v>
       </c>
       <c r="T70" t="n">
-        <v>554</v>
+        <v>558</v>
       </c>
     </row>
     <row r="71">
@@ -5189,7 +5189,7 @@
         <v>69</v>
       </c>
       <c r="P72" t="n">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="Q72" t="n">
         <v>0</v>
@@ -5201,7 +5201,7 @@
         <v>0</v>
       </c>
       <c r="T72" t="n">
-        <v>148</v>
+        <v>109</v>
       </c>
     </row>
     <row r="73">
@@ -5321,7 +5321,7 @@
         <v>58</v>
       </c>
       <c r="P74" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="Q74" t="n">
         <v>0</v>
@@ -5333,7 +5333,7 @@
         <v>0</v>
       </c>
       <c r="T74" t="n">
-        <v>342</v>
+        <v>294</v>
       </c>
     </row>
     <row r="75">
@@ -5387,7 +5387,7 @@
         <v>21</v>
       </c>
       <c r="P75" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="Q75" t="n">
         <v>0</v>
@@ -5399,7 +5399,7 @@
         <v>0</v>
       </c>
       <c r="T75" t="n">
-        <v>549</v>
+        <v>539</v>
       </c>
     </row>
     <row r="76">
@@ -5519,7 +5519,7 @@
         <v>43</v>
       </c>
       <c r="P77" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="Q77" t="n">
         <v>0</v>
@@ -5531,7 +5531,7 @@
         <v>0</v>
       </c>
       <c r="T77" t="n">
-        <v>615</v>
+        <v>586</v>
       </c>
     </row>
     <row r="78">
@@ -5585,7 +5585,7 @@
         <v>62</v>
       </c>
       <c r="P78" t="n">
-        <v>61</v>
+        <v>0</v>
       </c>
       <c r="Q78" t="n">
         <v>0</v>
@@ -5597,7 +5597,7 @@
         <v>0</v>
       </c>
       <c r="T78" t="n">
-        <v>156</v>
+        <v>95</v>
       </c>
     </row>
     <row r="79">
@@ -5651,7 +5651,7 @@
         <v>17</v>
       </c>
       <c r="P79" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="Q79" t="n">
         <v>0</v>
@@ -5663,7 +5663,7 @@
         <v>0</v>
       </c>
       <c r="T79" t="n">
-        <v>30</v>
+        <v>17</v>
       </c>
     </row>
     <row r="80">
@@ -7367,7 +7367,7 @@
         <v>39</v>
       </c>
       <c r="P105" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="Q105" t="n">
         <v>0</v>
@@ -7379,7 +7379,7 @@
         <v>0</v>
       </c>
       <c r="T105" t="n">
-        <v>447</v>
+        <v>422</v>
       </c>
     </row>
     <row r="106">
@@ -7499,7 +7499,7 @@
         <v>138</v>
       </c>
       <c r="P107" t="n">
-        <v>61</v>
+        <v>0</v>
       </c>
       <c r="Q107" t="n">
         <v>0</v>
@@ -7511,7 +7511,7 @@
         <v>0</v>
       </c>
       <c r="T107" t="n">
-        <v>461</v>
+        <v>400</v>
       </c>
     </row>
     <row r="108">
@@ -7565,7 +7565,7 @@
         <v>49</v>
       </c>
       <c r="P108" t="n">
-        <v>62</v>
+        <v>0</v>
       </c>
       <c r="Q108" t="n">
         <v>0</v>
@@ -7577,7 +7577,7 @@
         <v>0</v>
       </c>
       <c r="T108" t="n">
-        <v>278</v>
+        <v>216</v>
       </c>
     </row>
     <row r="109">
@@ -7697,7 +7697,7 @@
         <v>36</v>
       </c>
       <c r="P110" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="Q110" t="n">
         <v>0</v>
@@ -7709,7 +7709,7 @@
         <v>0</v>
       </c>
       <c r="T110" t="n">
-        <v>421</v>
+        <v>366</v>
       </c>
     </row>
     <row r="111">
@@ -8093,7 +8093,7 @@
         <v>2</v>
       </c>
       <c r="P116" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="Q116" t="n">
         <v>0</v>
@@ -8105,7 +8105,7 @@
         <v>0</v>
       </c>
       <c r="T116" t="n">
-        <v>553</v>
+        <v>526</v>
       </c>
     </row>
     <row r="117">
@@ -8357,7 +8357,7 @@
         <v>27</v>
       </c>
       <c r="P120" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="Q120" t="n">
         <v>0</v>
@@ -8369,7 +8369,7 @@
         <v>0</v>
       </c>
       <c r="T120" t="n">
-        <v>755</v>
+        <v>736</v>
       </c>
     </row>
     <row r="121">
@@ -8423,7 +8423,7 @@
         <v>23</v>
       </c>
       <c r="P121" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q121" t="n">
         <v>0</v>
@@ -8435,7 +8435,7 @@
         <v>0</v>
       </c>
       <c r="T121" t="n">
-        <v>422</v>
+        <v>420</v>
       </c>
     </row>
     <row r="122">
@@ -8489,7 +8489,7 @@
         <v>0</v>
       </c>
       <c r="P122" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Q122" t="n">
         <v>0</v>
@@ -8501,7 +8501,7 @@
         <v>0</v>
       </c>
       <c r="T122" t="n">
-        <v>55</v>
+        <v>51</v>
       </c>
     </row>
     <row r="123">
@@ -8555,7 +8555,7 @@
         <v>23</v>
       </c>
       <c r="P123" t="n">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="Q123" t="n">
         <v>0</v>
@@ -8567,7 +8567,7 @@
         <v>0</v>
       </c>
       <c r="T123" t="n">
-        <v>432</v>
+        <v>347</v>
       </c>
     </row>
     <row r="124">
@@ -8687,7 +8687,7 @@
         <v>0</v>
       </c>
       <c r="P125" t="n">
-        <v>69</v>
+        <v>0</v>
       </c>
       <c r="Q125" t="n">
         <v>0</v>
@@ -8699,7 +8699,7 @@
         <v>0</v>
       </c>
       <c r="T125" t="n">
-        <v>366</v>
+        <v>297</v>
       </c>
     </row>
     <row r="126">
@@ -8819,7 +8819,7 @@
         <v>24</v>
       </c>
       <c r="P127" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="Q127" t="n">
         <v>0</v>
@@ -8831,7 +8831,7 @@
         <v>0</v>
       </c>
       <c r="T127" t="n">
-        <v>629</v>
+        <v>606</v>
       </c>
     </row>
     <row r="128">
@@ -8885,7 +8885,7 @@
         <v>21</v>
       </c>
       <c r="P128" t="n">
-        <v>83</v>
+        <v>0</v>
       </c>
       <c r="Q128" t="n">
         <v>0</v>
@@ -8897,7 +8897,7 @@
         <v>0</v>
       </c>
       <c r="T128" t="n">
-        <v>289</v>
+        <v>206</v>
       </c>
     </row>
     <row r="129">
@@ -10337,7 +10337,7 @@
         <v>2</v>
       </c>
       <c r="P150" t="n">
-        <v>72</v>
+        <v>0</v>
       </c>
       <c r="Q150" t="n">
         <v>0</v>
@@ -10349,7 +10349,7 @@
         <v>0</v>
       </c>
       <c r="T150" t="n">
-        <v>421</v>
+        <v>349</v>
       </c>
     </row>
     <row r="151">
@@ -10403,7 +10403,7 @@
         <v>35</v>
       </c>
       <c r="P151" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="Q151" t="n">
         <v>0</v>
@@ -10415,7 +10415,7 @@
         <v>0</v>
       </c>
       <c r="T151" t="n">
-        <v>541</v>
+        <v>507</v>
       </c>
     </row>
     <row r="152">
@@ -10469,7 +10469,7 @@
         <v>82</v>
       </c>
       <c r="P152" t="n">
-        <v>71</v>
+        <v>0</v>
       </c>
       <c r="Q152" t="n">
         <v>0</v>
@@ -10481,7 +10481,7 @@
         <v>0</v>
       </c>
       <c r="T152" t="n">
-        <v>845</v>
+        <v>774</v>
       </c>
     </row>
     <row r="153">
@@ -10535,7 +10535,7 @@
         <v>43</v>
       </c>
       <c r="P153" t="n">
-        <v>146</v>
+        <v>0</v>
       </c>
       <c r="Q153" t="n">
         <v>0</v>
@@ -10547,7 +10547,7 @@
         <v>0</v>
       </c>
       <c r="T153" t="n">
-        <v>775</v>
+        <v>629</v>
       </c>
     </row>
     <row r="154">
@@ -10667,7 +10667,7 @@
         <v>4</v>
       </c>
       <c r="P155" t="n">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="Q155" t="n">
         <v>0</v>
@@ -10679,7 +10679,7 @@
         <v>0</v>
       </c>
       <c r="T155" t="n">
-        <v>132</v>
+        <v>89</v>
       </c>
     </row>
     <row r="156">
@@ -10733,7 +10733,7 @@
         <v>0</v>
       </c>
       <c r="P156" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="Q156" t="n">
         <v>0</v>
@@ -10745,7 +10745,7 @@
         <v>0</v>
       </c>
       <c r="T156" t="n">
-        <v>344</v>
+        <v>264</v>
       </c>
     </row>
     <row r="157">
@@ -10799,7 +10799,7 @@
         <v>0</v>
       </c>
       <c r="P157" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="Q157" t="n">
         <v>0</v>
@@ -10811,7 +10811,7 @@
         <v>0</v>
       </c>
       <c r="T157" t="n">
-        <v>499</v>
+        <v>477</v>
       </c>
     </row>
     <row r="158">
@@ -10865,7 +10865,7 @@
         <v>0</v>
       </c>
       <c r="P158" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="Q158" t="n">
         <v>0</v>
@@ -10877,7 +10877,7 @@
         <v>0</v>
       </c>
       <c r="T158" t="n">
-        <v>549</v>
+        <v>521</v>
       </c>
     </row>
     <row r="159">
@@ -11063,7 +11063,7 @@
         <v>4</v>
       </c>
       <c r="P161" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="Q161" t="n">
         <v>0</v>
@@ -11075,7 +11075,7 @@
         <v>0</v>
       </c>
       <c r="T161" t="n">
-        <v>139</v>
+        <v>130</v>
       </c>
     </row>
     <row r="162">
@@ -11393,7 +11393,7 @@
         <v>138</v>
       </c>
       <c r="P166" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="Q166" t="n">
         <v>0</v>
@@ -11405,7 +11405,7 @@
         <v>0</v>
       </c>
       <c r="T166" t="n">
-        <v>923</v>
+        <v>907</v>
       </c>
     </row>
     <row r="167">
@@ -11459,7 +11459,7 @@
         <v>79</v>
       </c>
       <c r="P167" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="Q167" t="n">
         <v>0</v>
@@ -11471,7 +11471,7 @@
         <v>0</v>
       </c>
       <c r="T167" t="n">
-        <v>651</v>
+        <v>609</v>
       </c>
     </row>
     <row r="168">
@@ -11525,7 +11525,7 @@
         <v>62</v>
       </c>
       <c r="P168" t="n">
-        <v>52</v>
+        <v>0</v>
       </c>
       <c r="Q168" t="n">
         <v>0</v>
@@ -11537,7 +11537,7 @@
         <v>0</v>
       </c>
       <c r="T168" t="n">
-        <v>238</v>
+        <v>186</v>
       </c>
     </row>
     <row r="169">

--- a/outputs/player_points_by_team_game.xlsx
+++ b/outputs/player_points_by_team_game.xlsx
@@ -1955,7 +1955,7 @@
         <v>70</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>107</v>
       </c>
       <c r="Q23" t="n">
         <v>0</v>
@@ -1967,7 +1967,7 @@
         <v>0</v>
       </c>
       <c r="T23" t="n">
-        <v>539</v>
+        <v>646</v>
       </c>
     </row>
     <row r="24">
@@ -2021,7 +2021,7 @@
         <v>76</v>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="Q24" t="n">
         <v>0</v>
@@ -2033,7 +2033,7 @@
         <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>127</v>
+        <v>157</v>
       </c>
     </row>
     <row r="25">
@@ -2087,7 +2087,7 @@
         <v>27</v>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>
@@ -2099,7 +2099,7 @@
         <v>0</v>
       </c>
       <c r="T25" t="n">
-        <v>258</v>
+        <v>290</v>
       </c>
     </row>
     <row r="26">
@@ -2219,7 +2219,7 @@
         <v>23</v>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="Q27" t="n">
         <v>0</v>
@@ -2231,7 +2231,7 @@
         <v>0</v>
       </c>
       <c r="T27" t="n">
-        <v>328</v>
+        <v>384</v>
       </c>
     </row>
     <row r="28">
@@ -2417,7 +2417,7 @@
         <v>77</v>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>91</v>
       </c>
       <c r="Q30" t="n">
         <v>0</v>
@@ -2429,7 +2429,7 @@
         <v>0</v>
       </c>
       <c r="T30" t="n">
-        <v>812</v>
+        <v>903</v>
       </c>
     </row>
     <row r="31">
@@ -2483,7 +2483,7 @@
         <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>83</v>
       </c>
       <c r="Q31" t="n">
         <v>0</v>
@@ -2495,7 +2495,7 @@
         <v>0</v>
       </c>
       <c r="T31" t="n">
-        <v>240</v>
+        <v>323</v>
       </c>
     </row>
     <row r="32">
@@ -2549,7 +2549,7 @@
         <v>66</v>
       </c>
       <c r="P32" t="n">
-        <v>0</v>
+        <v>91</v>
       </c>
       <c r="Q32" t="n">
         <v>0</v>
@@ -2561,7 +2561,7 @@
         <v>0</v>
       </c>
       <c r="T32" t="n">
-        <v>336</v>
+        <v>427</v>
       </c>
     </row>
     <row r="33">
@@ -2615,7 +2615,7 @@
         <v>56</v>
       </c>
       <c r="P33" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q33" t="n">
         <v>0</v>
@@ -2627,7 +2627,7 @@
         <v>0</v>
       </c>
       <c r="T33" t="n">
-        <v>138</v>
+        <v>140</v>
       </c>
     </row>
     <row r="34">
@@ -2681,7 +2681,7 @@
         <v>126</v>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="Q34" t="n">
         <v>0</v>
@@ -2693,7 +2693,7 @@
         <v>0</v>
       </c>
       <c r="T34" t="n">
-        <v>279</v>
+        <v>349</v>
       </c>
     </row>
     <row r="35">
@@ -3011,7 +3011,7 @@
         <v>14</v>
       </c>
       <c r="P39" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="Q39" t="n">
         <v>0</v>
@@ -3023,7 +3023,7 @@
         <v>0</v>
       </c>
       <c r="T39" t="n">
-        <v>44</v>
+        <v>79</v>
       </c>
     </row>
     <row r="40">
@@ -3077,7 +3077,7 @@
         <v>0</v>
       </c>
       <c r="P40" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="Q40" t="n">
         <v>0</v>
@@ -3089,7 +3089,7 @@
         <v>0</v>
       </c>
       <c r="T40" t="n">
-        <v>403</v>
+        <v>415</v>
       </c>
     </row>
     <row r="41">
@@ -3209,7 +3209,7 @@
         <v>16</v>
       </c>
       <c r="P42" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="Q42" t="n">
         <v>0</v>
@@ -3221,7 +3221,7 @@
         <v>0</v>
       </c>
       <c r="T42" t="n">
-        <v>447</v>
+        <v>459</v>
       </c>
     </row>
     <row r="43">
@@ -4661,7 +4661,7 @@
         <v>29</v>
       </c>
       <c r="P64" t="n">
-        <v>0</v>
+        <v>99</v>
       </c>
       <c r="Q64" t="n">
         <v>0</v>
@@ -4673,7 +4673,7 @@
         <v>0</v>
       </c>
       <c r="T64" t="n">
-        <v>451</v>
+        <v>550</v>
       </c>
     </row>
     <row r="65">
@@ -4727,7 +4727,7 @@
         <v>24</v>
       </c>
       <c r="P65" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="Q65" t="n">
         <v>0</v>
@@ -4739,7 +4739,7 @@
         <v>0</v>
       </c>
       <c r="T65" t="n">
-        <v>395</v>
+        <v>430</v>
       </c>
     </row>
     <row r="66">
@@ -4859,7 +4859,7 @@
         <v>66</v>
       </c>
       <c r="P67" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q67" t="n">
         <v>0</v>
@@ -4871,7 +4871,7 @@
         <v>0</v>
       </c>
       <c r="T67" t="n">
-        <v>705</v>
+        <v>709</v>
       </c>
     </row>
     <row r="68">
@@ -4925,7 +4925,7 @@
         <v>12</v>
       </c>
       <c r="P68" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="Q68" t="n">
         <v>0</v>
@@ -4937,7 +4937,7 @@
         <v>0</v>
       </c>
       <c r="T68" t="n">
-        <v>322</v>
+        <v>357</v>
       </c>
     </row>
     <row r="69">
@@ -4991,7 +4991,7 @@
         <v>14</v>
       </c>
       <c r="P69" t="n">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="Q69" t="n">
         <v>0</v>
@@ -5003,7 +5003,7 @@
         <v>0</v>
       </c>
       <c r="T69" t="n">
-        <v>505</v>
+        <v>546</v>
       </c>
     </row>
     <row r="70">
@@ -5057,7 +5057,7 @@
         <v>54</v>
       </c>
       <c r="P70" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="Q70" t="n">
         <v>0</v>
@@ -5069,7 +5069,7 @@
         <v>0</v>
       </c>
       <c r="T70" t="n">
-        <v>558</v>
+        <v>554</v>
       </c>
     </row>
     <row r="71">
@@ -5189,7 +5189,7 @@
         <v>69</v>
       </c>
       <c r="P72" t="n">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="Q72" t="n">
         <v>0</v>
@@ -5201,7 +5201,7 @@
         <v>0</v>
       </c>
       <c r="T72" t="n">
-        <v>109</v>
+        <v>148</v>
       </c>
     </row>
     <row r="73">
@@ -5321,7 +5321,7 @@
         <v>58</v>
       </c>
       <c r="P74" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="Q74" t="n">
         <v>0</v>
@@ -5333,7 +5333,7 @@
         <v>0</v>
       </c>
       <c r="T74" t="n">
-        <v>294</v>
+        <v>342</v>
       </c>
     </row>
     <row r="75">
@@ -5387,7 +5387,7 @@
         <v>21</v>
       </c>
       <c r="P75" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Q75" t="n">
         <v>0</v>
@@ -5399,7 +5399,7 @@
         <v>0</v>
       </c>
       <c r="T75" t="n">
-        <v>539</v>
+        <v>549</v>
       </c>
     </row>
     <row r="76">
@@ -5519,7 +5519,7 @@
         <v>43</v>
       </c>
       <c r="P77" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="Q77" t="n">
         <v>0</v>
@@ -5531,7 +5531,7 @@
         <v>0</v>
       </c>
       <c r="T77" t="n">
-        <v>586</v>
+        <v>615</v>
       </c>
     </row>
     <row r="78">
@@ -5585,7 +5585,7 @@
         <v>62</v>
       </c>
       <c r="P78" t="n">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="Q78" t="n">
         <v>0</v>
@@ -5597,7 +5597,7 @@
         <v>0</v>
       </c>
       <c r="T78" t="n">
-        <v>95</v>
+        <v>156</v>
       </c>
     </row>
     <row r="79">
@@ -5651,7 +5651,7 @@
         <v>17</v>
       </c>
       <c r="P79" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="Q79" t="n">
         <v>0</v>
@@ -5663,7 +5663,7 @@
         <v>0</v>
       </c>
       <c r="T79" t="n">
-        <v>17</v>
+        <v>30</v>
       </c>
     </row>
     <row r="80">
@@ -7367,7 +7367,7 @@
         <v>39</v>
       </c>
       <c r="P105" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="Q105" t="n">
         <v>0</v>
@@ -7379,7 +7379,7 @@
         <v>0</v>
       </c>
       <c r="T105" t="n">
-        <v>422</v>
+        <v>447</v>
       </c>
     </row>
     <row r="106">
@@ -7499,7 +7499,7 @@
         <v>138</v>
       </c>
       <c r="P107" t="n">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="Q107" t="n">
         <v>0</v>
@@ -7511,7 +7511,7 @@
         <v>0</v>
       </c>
       <c r="T107" t="n">
-        <v>400</v>
+        <v>461</v>
       </c>
     </row>
     <row r="108">
@@ -7565,7 +7565,7 @@
         <v>49</v>
       </c>
       <c r="P108" t="n">
-        <v>0</v>
+        <v>62</v>
       </c>
       <c r="Q108" t="n">
         <v>0</v>
@@ -7577,7 +7577,7 @@
         <v>0</v>
       </c>
       <c r="T108" t="n">
-        <v>216</v>
+        <v>278</v>
       </c>
     </row>
     <row r="109">
@@ -7697,7 +7697,7 @@
         <v>36</v>
       </c>
       <c r="P110" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="Q110" t="n">
         <v>0</v>
@@ -7709,7 +7709,7 @@
         <v>0</v>
       </c>
       <c r="T110" t="n">
-        <v>366</v>
+        <v>421</v>
       </c>
     </row>
     <row r="111">
@@ -8093,7 +8093,7 @@
         <v>2</v>
       </c>
       <c r="P116" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="Q116" t="n">
         <v>0</v>
@@ -8105,7 +8105,7 @@
         <v>0</v>
       </c>
       <c r="T116" t="n">
-        <v>526</v>
+        <v>553</v>
       </c>
     </row>
     <row r="117">
@@ -8357,7 +8357,7 @@
         <v>27</v>
       </c>
       <c r="P120" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="Q120" t="n">
         <v>0</v>
@@ -8369,7 +8369,7 @@
         <v>0</v>
       </c>
       <c r="T120" t="n">
-        <v>736</v>
+        <v>755</v>
       </c>
     </row>
     <row r="121">
@@ -8423,7 +8423,7 @@
         <v>23</v>
       </c>
       <c r="P121" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q121" t="n">
         <v>0</v>
@@ -8435,7 +8435,7 @@
         <v>0</v>
       </c>
       <c r="T121" t="n">
-        <v>420</v>
+        <v>422</v>
       </c>
     </row>
     <row r="122">
@@ -8489,7 +8489,7 @@
         <v>0</v>
       </c>
       <c r="P122" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q122" t="n">
         <v>0</v>
@@ -8501,7 +8501,7 @@
         <v>0</v>
       </c>
       <c r="T122" t="n">
-        <v>51</v>
+        <v>55</v>
       </c>
     </row>
     <row r="123">
@@ -8555,7 +8555,7 @@
         <v>23</v>
       </c>
       <c r="P123" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="Q123" t="n">
         <v>0</v>
@@ -8567,7 +8567,7 @@
         <v>0</v>
       </c>
       <c r="T123" t="n">
-        <v>347</v>
+        <v>432</v>
       </c>
     </row>
     <row r="124">
@@ -8687,7 +8687,7 @@
         <v>0</v>
       </c>
       <c r="P125" t="n">
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="Q125" t="n">
         <v>0</v>
@@ -8699,7 +8699,7 @@
         <v>0</v>
       </c>
       <c r="T125" t="n">
-        <v>297</v>
+        <v>366</v>
       </c>
     </row>
     <row r="126">
@@ -8819,7 +8819,7 @@
         <v>24</v>
       </c>
       <c r="P127" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="Q127" t="n">
         <v>0</v>
@@ -8831,7 +8831,7 @@
         <v>0</v>
       </c>
       <c r="T127" t="n">
-        <v>606</v>
+        <v>629</v>
       </c>
     </row>
     <row r="128">
@@ -8885,7 +8885,7 @@
         <v>21</v>
       </c>
       <c r="P128" t="n">
-        <v>0</v>
+        <v>83</v>
       </c>
       <c r="Q128" t="n">
         <v>0</v>
@@ -8897,7 +8897,7 @@
         <v>0</v>
       </c>
       <c r="T128" t="n">
-        <v>206</v>
+        <v>289</v>
       </c>
     </row>
     <row r="129">
@@ -10337,7 +10337,7 @@
         <v>2</v>
       </c>
       <c r="P150" t="n">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="Q150" t="n">
         <v>0</v>
@@ -10349,7 +10349,7 @@
         <v>0</v>
       </c>
       <c r="T150" t="n">
-        <v>349</v>
+        <v>421</v>
       </c>
     </row>
     <row r="151">
@@ -10403,7 +10403,7 @@
         <v>35</v>
       </c>
       <c r="P151" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="Q151" t="n">
         <v>0</v>
@@ -10415,7 +10415,7 @@
         <v>0</v>
       </c>
       <c r="T151" t="n">
-        <v>507</v>
+        <v>541</v>
       </c>
     </row>
     <row r="152">
@@ -10469,7 +10469,7 @@
         <v>82</v>
       </c>
       <c r="P152" t="n">
-        <v>0</v>
+        <v>71</v>
       </c>
       <c r="Q152" t="n">
         <v>0</v>
@@ -10481,7 +10481,7 @@
         <v>0</v>
       </c>
       <c r="T152" t="n">
-        <v>774</v>
+        <v>845</v>
       </c>
     </row>
     <row r="153">
@@ -10535,7 +10535,7 @@
         <v>43</v>
       </c>
       <c r="P153" t="n">
-        <v>0</v>
+        <v>146</v>
       </c>
       <c r="Q153" t="n">
         <v>0</v>
@@ -10547,7 +10547,7 @@
         <v>0</v>
       </c>
       <c r="T153" t="n">
-        <v>629</v>
+        <v>775</v>
       </c>
     </row>
     <row r="154">
@@ -10667,7 +10667,7 @@
         <v>4</v>
       </c>
       <c r="P155" t="n">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="Q155" t="n">
         <v>0</v>
@@ -10679,7 +10679,7 @@
         <v>0</v>
       </c>
       <c r="T155" t="n">
-        <v>89</v>
+        <v>132</v>
       </c>
     </row>
     <row r="156">
@@ -10733,7 +10733,7 @@
         <v>0</v>
       </c>
       <c r="P156" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="Q156" t="n">
         <v>0</v>
@@ -10745,7 +10745,7 @@
         <v>0</v>
       </c>
       <c r="T156" t="n">
-        <v>264</v>
+        <v>344</v>
       </c>
     </row>
     <row r="157">
@@ -10799,7 +10799,7 @@
         <v>0</v>
       </c>
       <c r="P157" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="Q157" t="n">
         <v>0</v>
@@ -10811,7 +10811,7 @@
         <v>0</v>
       </c>
       <c r="T157" t="n">
-        <v>477</v>
+        <v>499</v>
       </c>
     </row>
     <row r="158">
@@ -10865,7 +10865,7 @@
         <v>0</v>
       </c>
       <c r="P158" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="Q158" t="n">
         <v>0</v>
@@ -10877,7 +10877,7 @@
         <v>0</v>
       </c>
       <c r="T158" t="n">
-        <v>521</v>
+        <v>549</v>
       </c>
     </row>
     <row r="159">
@@ -11063,7 +11063,7 @@
         <v>4</v>
       </c>
       <c r="P161" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="Q161" t="n">
         <v>0</v>
@@ -11075,7 +11075,7 @@
         <v>0</v>
       </c>
       <c r="T161" t="n">
-        <v>130</v>
+        <v>139</v>
       </c>
     </row>
     <row r="162">
@@ -11393,7 +11393,7 @@
         <v>138</v>
       </c>
       <c r="P166" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="Q166" t="n">
         <v>0</v>
@@ -11405,7 +11405,7 @@
         <v>0</v>
       </c>
       <c r="T166" t="n">
-        <v>907</v>
+        <v>923</v>
       </c>
     </row>
     <row r="167">
@@ -11459,7 +11459,7 @@
         <v>79</v>
       </c>
       <c r="P167" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="Q167" t="n">
         <v>0</v>
@@ -11471,7 +11471,7 @@
         <v>0</v>
       </c>
       <c r="T167" t="n">
-        <v>609</v>
+        <v>651</v>
       </c>
     </row>
     <row r="168">
@@ -11525,7 +11525,7 @@
         <v>62</v>
       </c>
       <c r="P168" t="n">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="Q168" t="n">
         <v>0</v>
@@ -11537,7 +11537,7 @@
         <v>0</v>
       </c>
       <c r="T168" t="n">
-        <v>186</v>
+        <v>238</v>
       </c>
     </row>
     <row r="169">
